--- a/data/trans_dic/P22$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1137,57 +1137,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,07</t>
+          <t>0,08; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,63</t>
+          <t>0,05; 0,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,53</t>
+          <t>0,04; 0,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,17</t>
+          <t>0,15; 1,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,74</t>
+          <t>0,14; 0,75</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,43</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,46</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,46</t>
-        </is>
-      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,41</t>
+          <t>0,03; 0,43</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,49</t>
+          <t>0,05; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,29</t>
+          <t>0,04; 0,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,44</t>
+          <t>0,07; 0,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,17</t>
+          <t>0,0; 0,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,21</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,14</t>
+          <t>0,0; 0,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,23</t>
+          <t>0,02; 0,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,29</t>
+          <t>0,06; 0,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,27</t>
+          <t>0,04; 0,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,16</t>
+          <t>0,02; 0,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,28</t>
+          <t>0,06; 0,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,2</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6678</t>
+          <t>0; 6103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1251</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 6134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2120</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>0; 2254</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2134</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2104</t>
+          <t>0; 2462</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7620</t>
+          <t>0; 9117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1105</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 10057</t>
+          <t>0; 8911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1037; 13230</t>
+          <t>1040; 11270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2053</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8757</t>
+          <t>0; 9065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7913</t>
+          <t>0; 6580</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7398</t>
+          <t>0; 7352</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1526</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1037; 12324</t>
+          <t>1036; 14105</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6591</t>
+          <t>0; 6026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>851; 10512</t>
+          <t>852; 10237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4471</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8751</t>
+          <t>0; 8796</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 8219</t>
+          <t>0; 8553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5343</t>
+          <t>0; 4921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4326</t>
+          <t>0; 5053</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2077</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1247; 9851</t>
+          <t>1300; 10371</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 10513</t>
+          <t>0; 8897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7389</t>
+          <t>0; 8526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5310</t>
+          <t>0; 5988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1627; 9782</t>
+          <t>1796; 9797</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1865</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6363</t>
+          <t>0; 7163</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6072</t>
+          <t>0; 6077</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 816</t>
+          <t>0; 946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7947</t>
+          <t>0; 6159</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5427</t>
+          <t>0; 5475</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3927</t>
+          <t>0; 4355</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7097</t>
+          <t>0; 6655</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6314</t>
+          <t>0; 6351</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 9200</t>
+          <t>0; 8095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>164; 4078</t>
+          <t>314; 4312</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1658; 15848</t>
+          <t>1654; 16181</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1206; 9974</t>
+          <t>1210; 11891</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2281; 14804</t>
+          <t>2431; 15524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>173; 5848</t>
+          <t>161; 5828</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7092</t>
+          <t>0; 6729</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>0; 6002</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>850; 8198</t>
+          <t>852; 8798</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2277; 10429</t>
+          <t>2309; 10594</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3409; 17640</t>
+          <t>2811; 17087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1233; 11147</t>
+          <t>1232; 12994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4492; 19361</t>
+          <t>4421; 18914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3821; 14181</t>
+          <t>3633; 12943</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Clase-trans_dic.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,29</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,91</t>
+          <t>0,08; 1,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,72</t>
+          <t>0,05; 0,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,52</t>
+          <t>0,04; 0,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,24</t>
+          <t>0,16; 1,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,43</t>
+          <t>0,06; 1,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,5</t>
+          <t>0,05; 0,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,35</t>
+          <t>0,04; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,46</t>
+          <t>0,07; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,3</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,21</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,17</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,2</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,17</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,25</t>
+          <t>0,02; 0,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,3</t>
+          <t>0,08; 0,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,26</t>
+          <t>0,04; 0,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,19</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,07; 0,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,19</t>
+          <t>0,07; 0,28</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6103</t>
+          <t>0; 5685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6134</t>
+          <t>0; 6136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2254</t>
+          <t>0; 2396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2462</t>
+          <t>0; 1783</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9117</t>
+          <t>0; 8804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 8911</t>
+          <t>0; 8889</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1040; 11270</t>
+          <t>1033; 12586</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9065</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5136</t>
+          <t>0; 5648</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6580</t>
+          <t>0; 7329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7352</t>
+          <t>0; 7292</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1036; 14105</t>
+          <t>1037; 12200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6026</t>
+          <t>0; 6647</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>852; 10237</t>
+          <t>849; 9373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 6404</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5032</t>
         </is>
       </c>
     </row>
@@ -2759,22 +2759,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8796</t>
+          <t>0; 9617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 8553</t>
+          <t>0; 8610</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4921</t>
+          <t>0; 5325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5053</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2794,34 +2794,34 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1300; 10371</t>
+          <t>1352; 9723</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 8897</t>
+          <t>0; 10080</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 8526</t>
+          <t>0; 9297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 5295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1796; 9797</t>
+          <t>2002; 10436</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>3126</t>
         </is>
       </c>
     </row>
@@ -2972,22 +2972,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7163</t>
+          <t>0; 6409</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6077</t>
+          <t>0; 6717</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 946</t>
+          <t>0; 9656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6159</t>
+          <t>0; 7926</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5475</t>
+          <t>0; 5436</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4355</t>
+          <t>0; 4213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6655</t>
+          <t>0; 7114</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 8095</t>
+          <t>0; 7246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>314; 4312</t>
+          <t>686; 11173</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>9653</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1654; 16181</t>
+          <t>1754; 16585</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1210; 11891</t>
+          <t>1211; 11094</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2431; 15524</t>
+          <t>2357; 15226</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161; 5828</t>
+          <t>894; 10239</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6729</t>
+          <t>0; 7080</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6002</t>
+          <t>0; 6012</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>852; 8798</t>
+          <t>850; 9502</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2309; 10594</t>
+          <t>2806; 11998</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2811; 17087</t>
+          <t>2631; 18166</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1232; 12994</t>
+          <t>1234; 12334</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4421; 18914</t>
+          <t>4634; 19160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3633; 12943</t>
+          <t>4856; 19503</t>
         </is>
       </c>
     </row>
